--- a/questionnaire_templates/030_personal_finance_optimization_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/030_personal_finance_optimization_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>financial_goals</t>
+          <t>income_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financial Goals</t>
+          <t>Income Frequency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>income_range</t>
+          <t>spending_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Income Range</t>
+          <t>Spending Frequency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>income_frequency</t>
+          <t>money_savings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Income Frequency</t>
+          <t>Money Savings</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>income_frequency_2</t>
+          <t>emergency_funds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Income Frequency</t>
+          <t>Emergency Funds</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spending_frequency</t>
+          <t>bill_payment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spending Frequency</t>
+          <t>Bill Payment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>money_savings</t>
+          <t>savings_amount</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Money Savings</t>
+          <t>Savings Amount</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>money_savings_2</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Money Savings</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>money_savings_3</t>
+          <t>expense_tracking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Money Savings</t>
+          <t>Expense Tracking</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>money_savings_4</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Money Savings</t>
+          <t>Financial Planning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>money_savings_5</t>
+          <t>financial_advice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Money Savings</t>
+          <t>Financial Advice</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>money_savings_6</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>money_savings_7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>money_savings_8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>money_savings_9</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>money_savings_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>money_savings_11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>money_savings_12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>money_savings_13</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>money_savings_14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>money_savings_15</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>money_savings_16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>money_savings_17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>money_savings_18</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Money Savings</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_have_short-term_financial_goals</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I have short-term financial goals</t>
         </is>
       </c>
     </row>
@@ -1148,63 +849,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_have_long-term_financial_goals</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I have long-term financial goals</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>income_range_choices</t>
+          <t>financial_goals_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>i_do_not_have_financial_goals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>I do not have financial goals</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>income_range_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>income_range_choices</t>
+          <t>income_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1233,743 +934,301 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>irregular</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Irregular</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>income_frequency_choices</t>
+          <t>spending_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>income_frequency_2_choices</t>
+          <t>spending_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>income_frequency_2_choices</t>
+          <t>spending_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>income_frequency_2_choices</t>
+          <t>spending_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annually</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>spending_frequency_choices</t>
+          <t>money_savings_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>spending_frequency_choices</t>
+          <t>money_savings_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>spending_frequency_choices</t>
+          <t>emergency_funds_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>money_savings_choices</t>
+          <t>emergency_funds_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>money_savings_choices</t>
+          <t>bill_payment_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>On time</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>money_savings_2_choices</t>
+          <t>bill_payment_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>money_savings_2_choices</t>
+          <t>bill_payment_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>money_savings_3_choices</t>
+          <t>expense_tracking_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>money_savings_3_choices</t>
+          <t>expense_tracking_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>money_savings_4_choices</t>
+          <t>financial_planning_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>money_savings_4_choices</t>
+          <t>financial_planning_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>money_savings_5_choices</t>
+          <t>financial_advice_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>money_savings_5_choices</t>
+          <t>financial_advice_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>money_savings_6_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>money_savings_6_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>money_savings_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>money_savings_7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>money_savings_8_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>money_savings_8_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>money_savings_9_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>money_savings_9_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>money_savings_10_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>money_savings_10_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>money_savings_11_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>money_savings_11_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>money_savings_12_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>money_savings_12_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>money_savings_13_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>money_savings_13_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>money_savings_14_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>money_savings_14_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>money_savings_15_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>money_savings_15_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>money_savings_16_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>money_savings_16_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>money_savings_17_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>money_savings_17_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>money_savings_18_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>money_savings_18_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
